--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2023_antofagasta.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:45</t>
+    <t xml:space="preserve">2026-09-09 20:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2023_antofagasta.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2023_antofagasta.xlsx
@@ -27,21 +27,21 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calama</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:51</t>
+    <t xml:space="preserve">2026-09-18 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,7 +474,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
